--- a/Relatorio_Apostas_Completo_Otimizado.xlsx
+++ b/Relatorio_Apostas_Completo_Otimizado.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="34">
   <si>
     <t>Data_Hora</t>
   </si>
@@ -49,40 +49,16 @@
     <t>Lucro/Prejuízo</t>
   </si>
   <si>
-    <t>Corinthians</t>
+    <t>Cuiabá</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>Grêmio</t>
   </si>
   <si>
     <t>Vitória</t>
-  </si>
-  <si>
-    <t>Atlético-GO</t>
-  </si>
-  <si>
-    <t>Athletico-PR</t>
-  </si>
-  <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>Atlético-MG</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
-    <t>Vasco</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
-    <t>Grêmio</t>
   </si>
   <si>
     <t>Sport</t>
@@ -94,16 +70,34 @@
     <t>Red Bull Bragantino</t>
   </si>
   <si>
-    <t>Ceará</t>
+    <t>Vasco</t>
+  </si>
+  <si>
+    <t>Atlético-MG</t>
+  </si>
+  <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
   </si>
   <si>
     <t>Fluminense</t>
   </si>
   <si>
-    <t>Juventude</t>
+    <t>Ceará</t>
+  </si>
+  <si>
+    <t>Internacional</t>
   </si>
   <si>
     <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
   </si>
   <si>
     <t>Bahia</t>
@@ -112,10 +106,16 @@
     <t>Palmeiras</t>
   </si>
   <si>
-    <t>Flamengo</t>
+    <t>São Paulo</t>
   </si>
   <si>
-    <t>Santos</t>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>Flamengo</t>
   </si>
 </sst>
 </file>
@@ -477,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -517,69 +517,69 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2">
-        <v>45600.83333333334</v>
+        <v>45634.66666666666</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G2">
-        <v>2.49</v>
+        <v>2.84</v>
       </c>
       <c r="H2">
-        <v>32.26</v>
+        <v>28.57</v>
       </c>
       <c r="I2">
-        <v>40.23</v>
+        <v>35.15</v>
       </c>
       <c r="J2">
-        <v>24.71</v>
+        <v>23.03</v>
       </c>
       <c r="K2">
-        <v>2.1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2">
-        <v>45605.6875</v>
+        <v>45634.66666666666</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="G3">
-        <v>2.26</v>
+        <v>1.71</v>
       </c>
       <c r="H3">
-        <v>32.26</v>
+        <v>47.62</v>
       </c>
       <c r="I3">
-        <v>44.23</v>
+        <v>58.39</v>
       </c>
       <c r="J3">
-        <v>37.12</v>
+        <v>22.62</v>
       </c>
       <c r="K3">
         <v>-1</v>
@@ -587,83 +587,83 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2">
-        <v>45605.79166666666</v>
+        <v>45745.77083333334</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="G4">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="H4">
-        <v>38.46</v>
+        <v>36.36</v>
       </c>
       <c r="I4">
-        <v>50.59</v>
+        <v>48.53</v>
       </c>
       <c r="J4">
-        <v>31.53</v>
+        <v>33.46</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2">
-        <v>45612.77083333334</v>
+        <v>45753.77083333334</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>2.3</v>
+        <v>5.25</v>
       </c>
       <c r="G5">
-        <v>1.76</v>
+        <v>2.47</v>
       </c>
       <c r="H5">
-        <v>43.48</v>
+        <v>19.05</v>
       </c>
       <c r="I5">
-        <v>56.67</v>
+        <v>40.54</v>
       </c>
       <c r="J5">
-        <v>30.35</v>
+        <v>112.84</v>
       </c>
       <c r="K5">
-        <v>1.3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2">
-        <v>45616.79166666666</v>
+        <v>45753.77083333334</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -672,19 +672,19 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>3.28</v>
+        <v>2.29</v>
       </c>
       <c r="H6">
-        <v>23.09</v>
+        <v>33.33</v>
       </c>
       <c r="I6">
-        <v>30.47</v>
+        <v>43.72</v>
       </c>
       <c r="J6">
-        <v>31.91</v>
+        <v>31.17</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -692,34 +692,34 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2">
-        <v>45616.89583333334</v>
+        <v>45753.77083333334</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="G7">
-        <v>3.18</v>
+        <v>1.69</v>
       </c>
       <c r="H7">
-        <v>25.64</v>
+        <v>43.48</v>
       </c>
       <c r="I7">
-        <v>31.42</v>
+        <v>59.3</v>
       </c>
       <c r="J7">
-        <v>22.54</v>
+        <v>36.4</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -727,69 +727,69 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2">
-        <v>45619.8125</v>
+        <v>45759.66666666666</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="H8">
-        <v>12.5</v>
+        <v>33.33</v>
       </c>
       <c r="I8">
-        <v>42.61</v>
+        <v>52.43</v>
       </c>
       <c r="J8">
-        <v>240.87</v>
+        <v>57.3</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2">
-        <v>45619.89583333334</v>
+        <v>45760.72916666666</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="G9">
-        <v>1.58</v>
+        <v>3.35</v>
       </c>
       <c r="H9">
-        <v>51.28</v>
+        <v>22.22</v>
       </c>
       <c r="I9">
-        <v>63.44</v>
+        <v>29.89</v>
       </c>
       <c r="J9">
-        <v>23.71</v>
+        <v>34.52</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -797,69 +797,69 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2">
-        <v>45622.83333333334</v>
+        <v>45763.79166666666</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>2.33</v>
+        <v>1.54</v>
       </c>
       <c r="H10">
-        <v>32.26</v>
+        <v>33.33</v>
       </c>
       <c r="I10">
-        <v>42.85</v>
+        <v>64.97</v>
       </c>
       <c r="J10">
-        <v>32.85</v>
+        <v>94.91</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2">
-        <v>45626.8125</v>
+        <v>45766.77083333334</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>4.33</v>
+        <v>8.5</v>
       </c>
       <c r="G11">
-        <v>3.17</v>
+        <v>3.62</v>
       </c>
       <c r="H11">
-        <v>23.09</v>
+        <v>11.76</v>
       </c>
       <c r="I11">
-        <v>31.56</v>
+        <v>27.65</v>
       </c>
       <c r="J11">
-        <v>36.66</v>
+        <v>135.04</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -867,83 +867,83 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2">
-        <v>45630.79166666666</v>
+        <v>45766.875</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G12">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="H12">
-        <v>33.33</v>
+        <v>29.41</v>
       </c>
       <c r="I12">
-        <v>40.66</v>
+        <v>42.49</v>
       </c>
       <c r="J12">
-        <v>21.98</v>
+        <v>44.47</v>
       </c>
       <c r="K12">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2">
-        <v>45630.83333333334</v>
+        <v>45767.66666666666</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="G13">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="H13">
-        <v>40.82</v>
+        <v>45.45</v>
       </c>
       <c r="I13">
-        <v>58.73</v>
+        <v>56.85</v>
       </c>
       <c r="J13">
-        <v>43.88</v>
+        <v>25.07</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2">
-        <v>45630.89583333334</v>
+        <v>45767.77083333334</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -952,19 +952,19 @@
         <v>2</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G14">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="H14">
-        <v>25</v>
+        <v>24.39</v>
       </c>
       <c r="I14">
-        <v>47.12</v>
+        <v>36.99</v>
       </c>
       <c r="J14">
-        <v>88.48999999999999</v>
+        <v>51.68</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -972,104 +972,104 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2">
-        <v>45630.89583333334</v>
+        <v>45767.85416666666</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="G15">
-        <v>2.31</v>
+        <v>1.69</v>
       </c>
       <c r="H15">
-        <v>37.04</v>
+        <v>46.51</v>
       </c>
       <c r="I15">
-        <v>43.34</v>
+        <v>59.03</v>
       </c>
       <c r="J15">
-        <v>17.02</v>
+        <v>26.9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2">
-        <v>45745.77083333334</v>
+        <v>45773.77083333334</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="G16">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="H16">
-        <v>36.36</v>
+        <v>30.3</v>
       </c>
       <c r="I16">
-        <v>48.04</v>
+        <v>44.88</v>
       </c>
       <c r="J16">
-        <v>32.1</v>
+        <v>48.12</v>
       </c>
       <c r="K16">
-        <v>1.75</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2">
-        <v>45753.77083333334</v>
+        <v>45781.66666666666</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>2.3</v>
+        <v>3.22</v>
       </c>
       <c r="H17">
-        <v>33.33</v>
+        <v>14.29</v>
       </c>
       <c r="I17">
-        <v>43.49</v>
+        <v>31.04</v>
       </c>
       <c r="J17">
-        <v>30.46</v>
+        <v>117.31</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -1077,69 +1077,69 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2">
-        <v>45753.77083333334</v>
+        <v>45787.77083333334</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="G18">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="H18">
-        <v>43.48</v>
+        <v>35.71</v>
       </c>
       <c r="I18">
-        <v>54.31</v>
+        <v>56.13</v>
       </c>
       <c r="J18">
-        <v>24.9</v>
+        <v>57.16</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2">
-        <v>45753.77083333334</v>
+        <v>45789.83333333334</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>5.25</v>
+        <v>2.4</v>
       </c>
       <c r="G19">
-        <v>2.69</v>
+        <v>1.96</v>
       </c>
       <c r="H19">
-        <v>19.05</v>
+        <v>41.67</v>
       </c>
       <c r="I19">
-        <v>37.22</v>
+        <v>50.97</v>
       </c>
       <c r="J19">
-        <v>95.41</v>
+        <v>22.33</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -1147,10 +1147,10 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2">
-        <v>45759.66666666666</v>
+        <v>45795.77083333334</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
         <v>29</v>
@@ -1159,57 +1159,57 @@
         <v>1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="H20">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="I20">
-        <v>46.55</v>
+        <v>44.82</v>
       </c>
       <c r="J20">
-        <v>39.64</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2">
-        <v>45760.72916666666</v>
+        <v>45795.85416666666</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="G21">
-        <v>3.35</v>
+        <v>1.84</v>
       </c>
       <c r="H21">
-        <v>22.22</v>
+        <v>38.46</v>
       </c>
       <c r="I21">
-        <v>29.89</v>
+        <v>54.49</v>
       </c>
       <c r="J21">
-        <v>34.49</v>
+        <v>41.68</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -1217,16 +1217,16 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2">
-        <v>45763.79166666666</v>
+        <v>45809.8125</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1235,16 +1235,16 @@
         <v>3</v>
       </c>
       <c r="G22">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="H22">
         <v>33.33</v>
       </c>
       <c r="I22">
-        <v>61.49</v>
+        <v>59.59</v>
       </c>
       <c r="J22">
-        <v>84.48</v>
+        <v>78.78</v>
       </c>
       <c r="K22">
         <v>2</v>
@@ -1252,34 +1252,34 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2">
-        <v>45766.77083333334</v>
+        <v>45850.77083333334</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="G23">
-        <v>4.09</v>
+        <v>2.07</v>
       </c>
       <c r="H23">
-        <v>11.76</v>
+        <v>27.78</v>
       </c>
       <c r="I23">
-        <v>24.48</v>
+        <v>48.23</v>
       </c>
       <c r="J23">
-        <v>108.06</v>
+        <v>73.62</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -1287,69 +1287,69 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2">
-        <v>45767.66666666666</v>
+        <v>45857.77083333334</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G24">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="H24">
-        <v>45.45</v>
+        <v>37.04</v>
       </c>
       <c r="I24">
-        <v>57.04</v>
+        <v>49.11</v>
       </c>
       <c r="J24">
-        <v>25.5</v>
+        <v>32.6</v>
       </c>
       <c r="K24">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2">
-        <v>45767.77083333334</v>
+        <v>45858.72916666666</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="G25">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="H25">
-        <v>24.39</v>
+        <v>26.67</v>
       </c>
       <c r="I25">
-        <v>38.21</v>
+        <v>34.03</v>
       </c>
       <c r="J25">
-        <v>56.66</v>
+        <v>27.62</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -1357,69 +1357,69 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2">
-        <v>45767.85416666666</v>
+        <v>45861.79166666666</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="G26">
-        <v>1.56</v>
+        <v>2.26</v>
       </c>
       <c r="H26">
-        <v>46.51</v>
+        <v>34.72</v>
       </c>
       <c r="I26">
-        <v>63.97</v>
+        <v>44.34</v>
       </c>
       <c r="J26">
-        <v>37.55</v>
+        <v>27.69</v>
       </c>
       <c r="K26">
-        <v>1.15</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2">
-        <v>45773.77083333334</v>
+        <v>45862.79166666666</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="G27">
-        <v>2.33</v>
+        <v>2.74</v>
       </c>
       <c r="H27">
-        <v>30.3</v>
+        <v>21.05</v>
       </c>
       <c r="I27">
-        <v>42.93</v>
+        <v>36.49</v>
       </c>
       <c r="J27">
-        <v>41.66</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -1427,34 +1427,34 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2">
-        <v>45781.66666666666</v>
+        <v>45864.77083333334</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="G28">
-        <v>2.95</v>
+        <v>1.79</v>
       </c>
       <c r="H28">
-        <v>14.29</v>
+        <v>37.04</v>
       </c>
       <c r="I28">
-        <v>33.89</v>
+        <v>55.76</v>
       </c>
       <c r="J28">
-        <v>137.24</v>
+        <v>50.54</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -1462,69 +1462,69 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2">
-        <v>45787.77083333334</v>
+        <v>45872.77083333334</v>
       </c>
       <c r="B29" t="s">
         <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="G29">
-        <v>1.86</v>
+        <v>2.81</v>
       </c>
       <c r="H29">
-        <v>35.71</v>
+        <v>18.18</v>
       </c>
       <c r="I29">
-        <v>53.67</v>
+        <v>35.53</v>
       </c>
       <c r="J29">
-        <v>50.26</v>
+        <v>95.41</v>
       </c>
       <c r="K29">
-        <v>1.8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2">
-        <v>45795.77083333334</v>
+        <v>45879.66666666666</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="G30">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="H30">
-        <v>25</v>
+        <v>35.71</v>
       </c>
       <c r="I30">
-        <v>45.09</v>
+        <v>50.38</v>
       </c>
       <c r="J30">
-        <v>80.37</v>
+        <v>41.06</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -1532,69 +1532,69 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2">
-        <v>45795.85416666666</v>
+        <v>45880.83333333334</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>2.93</v>
       </c>
       <c r="H31">
-        <v>38.46</v>
+        <v>24.39</v>
       </c>
       <c r="I31">
-        <v>50.02</v>
+        <v>34.11</v>
       </c>
       <c r="J31">
-        <v>30.05</v>
+        <v>39.84</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2">
-        <v>45809.77083333334</v>
+        <v>45886.77083333334</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="G32">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="H32">
-        <v>36.36</v>
+        <v>22.22</v>
       </c>
       <c r="I32">
-        <v>47.19</v>
+        <v>42.83</v>
       </c>
       <c r="J32">
-        <v>29.76</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -1602,139 +1602,139 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2">
-        <v>45809.8125</v>
+        <v>45886.85416666666</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="G33">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="H33">
-        <v>33.33</v>
+        <v>34.72</v>
       </c>
       <c r="I33">
-        <v>61.56</v>
+        <v>46.37</v>
       </c>
       <c r="J33">
-        <v>84.67</v>
+        <v>33.54</v>
       </c>
       <c r="K33">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2">
-        <v>45850.77083333334</v>
+        <v>45889.79166666666</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="G34">
-        <v>2.14</v>
+        <v>3.14</v>
       </c>
       <c r="H34">
-        <v>27.78</v>
+        <v>24.39</v>
       </c>
       <c r="I34">
-        <v>46.65</v>
+        <v>31.87</v>
       </c>
       <c r="J34">
-        <v>67.95</v>
+        <v>30.68</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2">
-        <v>45857.77083333334</v>
+        <v>45893.77083333334</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
         <v>3</v>
       </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
       <c r="F35">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="G35">
-        <v>2.14</v>
+        <v>2.94</v>
       </c>
       <c r="H35">
-        <v>37.04</v>
+        <v>27.03</v>
       </c>
       <c r="I35">
-        <v>46.66</v>
+        <v>34</v>
       </c>
       <c r="J35">
-        <v>25.99</v>
+        <v>25.8</v>
       </c>
       <c r="K35">
-        <v>1.7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2">
-        <v>45858.72916666666</v>
+        <v>45900.77083333334</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
         <v>29</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G36">
-        <v>3.18</v>
+        <v>2.36</v>
       </c>
       <c r="H36">
-        <v>26.67</v>
+        <v>27.03</v>
       </c>
       <c r="I36">
-        <v>31.44</v>
+        <v>42.29</v>
       </c>
       <c r="J36">
-        <v>17.92</v>
+        <v>56.49</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -1742,34 +1742,34 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="2">
-        <v>45861.79166666666</v>
+        <v>45914.66666666666</v>
       </c>
       <c r="B37" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37">
-        <v>2.88</v>
+        <v>9</v>
       </c>
       <c r="G37">
-        <v>2.28</v>
+        <v>3.77</v>
       </c>
       <c r="H37">
-        <v>34.72</v>
+        <v>11.11</v>
       </c>
       <c r="I37">
-        <v>43.85</v>
+        <v>26.52</v>
       </c>
       <c r="J37">
-        <v>26.29</v>
+        <v>138.65</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -1777,34 +1777,34 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="2">
-        <v>45861.89583333334</v>
+        <v>45920.77083333334</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="G38">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="H38">
-        <v>23.81</v>
+        <v>34.72</v>
       </c>
       <c r="I38">
-        <v>30.35</v>
+        <v>47.73</v>
       </c>
       <c r="J38">
-        <v>27.45</v>
+        <v>37.47</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -1812,69 +1812,69 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="2">
-        <v>45862.79166666666</v>
+        <v>45927.77083333334</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>4.75</v>
+        <v>2.88</v>
       </c>
       <c r="G39">
-        <v>2.91</v>
+        <v>2.07</v>
       </c>
       <c r="H39">
-        <v>21.05</v>
+        <v>34.72</v>
       </c>
       <c r="I39">
-        <v>34.32</v>
+        <v>48.34</v>
       </c>
       <c r="J39">
-        <v>63.01</v>
+        <v>39.22</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="2">
-        <v>45864.77083333334</v>
+        <v>45927.77083333334</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G40">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="H40">
-        <v>37.04</v>
+        <v>31.25</v>
       </c>
       <c r="I40">
-        <v>55.81</v>
+        <v>48.17</v>
       </c>
       <c r="J40">
-        <v>50.67</v>
+        <v>54.16</v>
       </c>
       <c r="K40">
         <v>-1</v>
@@ -1882,34 +1882,34 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="2">
-        <v>45872.66666666666</v>
+        <v>45931.79166666666</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="G41">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="H41">
-        <v>43.48</v>
+        <v>57.14</v>
       </c>
       <c r="I41">
-        <v>53.14</v>
+        <v>70.38</v>
       </c>
       <c r="J41">
-        <v>22.21</v>
+        <v>23.17</v>
       </c>
       <c r="K41">
         <v>-1</v>
@@ -1917,104 +1917,104 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="2">
-        <v>45872.77083333334</v>
+        <v>45935.77083333334</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="G42">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="H42">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="I42">
-        <v>36.32</v>
+        <v>30.29</v>
       </c>
       <c r="J42">
-        <v>99.75</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="2">
-        <v>45872.85416666666</v>
+        <v>45938.875</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="G43">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="H43">
-        <v>40.82</v>
+        <v>34.48</v>
       </c>
       <c r="I43">
-        <v>48.29</v>
+        <v>43.82</v>
       </c>
       <c r="J43">
-        <v>18.32</v>
+        <v>27.08</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="2">
-        <v>45879.66666666666</v>
+        <v>45945.8125</v>
       </c>
       <c r="B44" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="G44">
-        <v>2.01</v>
+        <v>2.59</v>
       </c>
       <c r="H44">
-        <v>35.71</v>
+        <v>22.22</v>
       </c>
       <c r="I44">
-        <v>49.66</v>
+        <v>38.59</v>
       </c>
       <c r="J44">
-        <v>39.06</v>
+        <v>73.66</v>
       </c>
       <c r="K44">
         <v>-1</v>
@@ -2022,69 +2022,69 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="2">
-        <v>45880.83333333334</v>
+        <v>45945.83333333334</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45">
-        <v>4.1</v>
+        <v>2.35</v>
       </c>
       <c r="G45">
-        <v>3.12</v>
+        <v>1.88</v>
       </c>
       <c r="H45">
-        <v>24.39</v>
+        <v>42.55</v>
       </c>
       <c r="I45">
-        <v>32.08</v>
+        <v>53.17</v>
       </c>
       <c r="J45">
-        <v>31.54</v>
+        <v>24.94</v>
       </c>
       <c r="K45">
-        <v>3.1</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="2">
-        <v>45886.77083333334</v>
+        <v>45945.89583333334</v>
       </c>
       <c r="B46" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D46">
         <v>1</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="G46">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="H46">
-        <v>22.22</v>
+        <v>29.41</v>
       </c>
       <c r="I46">
-        <v>41.74</v>
+        <v>39.3</v>
       </c>
       <c r="J46">
-        <v>87.83</v>
+        <v>33.63</v>
       </c>
       <c r="K46">
         <v>-1</v>
@@ -2092,48 +2092,48 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="2">
-        <v>45886.85416666666</v>
+        <v>45945.89583333334</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C47" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="G47">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="H47">
-        <v>34.72</v>
+        <v>47.62</v>
       </c>
       <c r="I47">
-        <v>47.98</v>
+        <v>58.58</v>
       </c>
       <c r="J47">
-        <v>38.17</v>
+        <v>23.03</v>
       </c>
       <c r="K47">
-        <v>-1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="2">
-        <v>45889.79166666666</v>
+        <v>45946.79166666666</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -2142,54 +2142,54 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="G48">
-        <v>3.28</v>
+        <v>2.39</v>
       </c>
       <c r="H48">
-        <v>24.39</v>
+        <v>32.26</v>
       </c>
       <c r="I48">
-        <v>30.45</v>
+        <v>41.81</v>
       </c>
       <c r="J48">
-        <v>24.86</v>
+        <v>29.62</v>
       </c>
       <c r="K48">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="2">
-        <v>45893.77083333334</v>
+        <v>45949.77083333334</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="G49">
-        <v>3.09</v>
+        <v>1.87</v>
       </c>
       <c r="H49">
-        <v>27.03</v>
+        <v>41.67</v>
       </c>
       <c r="I49">
-        <v>32.4</v>
+        <v>53.43</v>
       </c>
       <c r="J49">
-        <v>19.87</v>
+        <v>28.24</v>
       </c>
       <c r="K49">
         <v>-1</v>
@@ -2197,209 +2197,209 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="2">
-        <v>45900.77083333334</v>
+        <v>45949.77083333334</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="G50">
-        <v>2.49</v>
+        <v>1.54</v>
       </c>
       <c r="H50">
-        <v>27.03</v>
+        <v>38.02</v>
       </c>
       <c r="I50">
-        <v>40.23</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="J50">
-        <v>48.86</v>
+        <v>70.69</v>
       </c>
       <c r="K50">
-        <v>-1</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="2">
-        <v>45914.66666666666</v>
+        <v>45950.79166666666</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="G51">
-        <v>3.91</v>
+        <v>2.09</v>
       </c>
       <c r="H51">
-        <v>11.11</v>
+        <v>31.25</v>
       </c>
       <c r="I51">
-        <v>25.56</v>
+        <v>47.83</v>
       </c>
       <c r="J51">
-        <v>130.02</v>
+        <v>53.04</v>
       </c>
       <c r="K51">
-        <v>-1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="2">
-        <v>45915.83333333334</v>
+        <v>45950.8125</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G52">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H52">
-        <v>33.33</v>
+        <v>30.3</v>
       </c>
       <c r="I52">
-        <v>39.96</v>
+        <v>38.49</v>
       </c>
       <c r="J52">
-        <v>19.87</v>
+        <v>27.03</v>
       </c>
       <c r="K52">
-        <v>-1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="2">
-        <v>45920.77083333334</v>
+        <v>45955.8125</v>
       </c>
       <c r="B53" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D53">
         <v>1</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>2.88</v>
+        <v>5.25</v>
       </c>
       <c r="G53">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="H53">
-        <v>34.72</v>
+        <v>19.05</v>
       </c>
       <c r="I53">
-        <v>48.86</v>
+        <v>50.2</v>
       </c>
       <c r="J53">
-        <v>40.73</v>
+        <v>163.54</v>
       </c>
       <c r="K53">
-        <v>-1</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="2">
-        <v>45927.77083333334</v>
+        <v>45956.85416666666</v>
       </c>
       <c r="B54" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C54" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E54">
         <v>0</v>
       </c>
       <c r="F54">
-        <v>2.88</v>
+        <v>1.65</v>
       </c>
       <c r="G54">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="H54">
-        <v>34.72</v>
+        <v>60.61</v>
       </c>
       <c r="I54">
-        <v>48.58</v>
+        <v>79.8</v>
       </c>
       <c r="J54">
-        <v>39.92</v>
+        <v>31.66</v>
       </c>
       <c r="K54">
-        <v>1.88</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="2">
-        <v>45927.77083333334</v>
+        <v>45962.75</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="G55">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="H55">
-        <v>31.25</v>
+        <v>42.55</v>
       </c>
       <c r="I55">
-        <v>44.7</v>
+        <v>60.86</v>
       </c>
       <c r="J55">
-        <v>43.04</v>
+        <v>43.03</v>
       </c>
       <c r="K55">
         <v>-1</v>
@@ -2407,69 +2407,69 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="2">
-        <v>45928.85416666666</v>
+        <v>45963.66666666666</v>
       </c>
       <c r="B56" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G56">
-        <v>3.56</v>
+        <v>2.32</v>
       </c>
       <c r="H56">
-        <v>20</v>
+        <v>33.33</v>
       </c>
       <c r="I56">
-        <v>28.08</v>
+        <v>43.16</v>
       </c>
       <c r="J56">
-        <v>40.41</v>
+        <v>29.49</v>
       </c>
       <c r="K56">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="2">
-        <v>45931.79166666666</v>
+        <v>45963.77083333334</v>
       </c>
       <c r="B57" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E57">
         <v>2</v>
       </c>
       <c r="F57">
-        <v>3.6</v>
+        <v>6.25</v>
       </c>
       <c r="G57">
-        <v>2.6</v>
+        <v>4.21</v>
       </c>
       <c r="H57">
-        <v>27.78</v>
+        <v>16</v>
       </c>
       <c r="I57">
-        <v>38.53</v>
+        <v>23.75</v>
       </c>
       <c r="J57">
-        <v>38.7</v>
+        <v>48.45</v>
       </c>
       <c r="K57">
         <v>-1</v>
@@ -2477,34 +2477,34 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="2">
-        <v>45931.79166666666</v>
+        <v>45963.85416666666</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="G58">
-        <v>1.45</v>
+        <v>1.82</v>
       </c>
       <c r="H58">
-        <v>57.14</v>
+        <v>44.44</v>
       </c>
       <c r="I58">
-        <v>68.78</v>
+        <v>54.94</v>
       </c>
       <c r="J58">
-        <v>20.37</v>
+        <v>23.62</v>
       </c>
       <c r="K58">
         <v>-1</v>
@@ -2512,13 +2512,13 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="2">
-        <v>45935.77083333334</v>
+        <v>45966.79166666666</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C59" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2527,89 +2527,89 @@
         <v>0</v>
       </c>
       <c r="F59">
-        <v>5.75</v>
+        <v>2.5</v>
       </c>
       <c r="G59">
-        <v>3.29</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>17.39</v>
+        <v>40</v>
       </c>
       <c r="I59">
-        <v>30.38</v>
+        <v>50.02</v>
       </c>
       <c r="J59">
-        <v>74.7</v>
+        <v>25.05</v>
       </c>
       <c r="K59">
-        <v>4.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="2">
-        <v>45938.875</v>
+        <v>45966.83333333334</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E60">
         <v>1</v>
       </c>
       <c r="F60">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G60">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H60">
-        <v>34.48</v>
+        <v>29.41</v>
       </c>
       <c r="I60">
-        <v>46.79</v>
+        <v>46.28</v>
       </c>
       <c r="J60">
-        <v>35.69</v>
+        <v>57.36</v>
       </c>
       <c r="K60">
-        <v>1.9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="2">
-        <v>45945.8125</v>
+        <v>45966.89583333334</v>
       </c>
       <c r="B61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C61" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="G61">
-        <v>2.62</v>
+        <v>2.93</v>
       </c>
       <c r="H61">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="I61">
-        <v>38.18</v>
+        <v>34.13</v>
       </c>
       <c r="J61">
-        <v>71.81</v>
+        <v>62.14</v>
       </c>
       <c r="K61">
         <v>-1</v>
@@ -2617,174 +2617,174 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="2">
-        <v>45945.83333333334</v>
+        <v>45970.66666666666</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
         <v>3</v>
       </c>
-      <c r="E62">
-        <v>1</v>
-      </c>
-      <c r="F62">
-        <v>2.35</v>
-      </c>
       <c r="G62">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="H62">
-        <v>42.55</v>
+        <v>33.33</v>
       </c>
       <c r="I62">
-        <v>53.29</v>
+        <v>43.2</v>
       </c>
       <c r="J62">
-        <v>25.23</v>
+        <v>29.6</v>
       </c>
       <c r="K62">
-        <v>1.35</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2">
-        <v>45945.89583333334</v>
+        <v>45970.85416666666</v>
       </c>
       <c r="B63" t="s">
         <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="G63">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="H63">
-        <v>29.41</v>
+        <v>25</v>
       </c>
       <c r="I63">
-        <v>35.67</v>
+        <v>34.56</v>
       </c>
       <c r="J63">
-        <v>21.29</v>
+        <v>38.24</v>
       </c>
       <c r="K63">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="2">
-        <v>45946.79166666666</v>
+        <v>45976.77083333334</v>
       </c>
       <c r="B64" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F64">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="G64">
-        <v>2.39</v>
+        <v>3.93</v>
       </c>
       <c r="H64">
-        <v>32.26</v>
+        <v>13.33</v>
       </c>
       <c r="I64">
-        <v>41.79</v>
+        <v>25.42</v>
       </c>
       <c r="J64">
-        <v>29.55</v>
+        <v>90.63</v>
       </c>
       <c r="K64">
-        <v>2.1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="2">
-        <v>45949.77083333334</v>
+        <v>45981.66666666666</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D65">
         <v>3</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F65">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="G65">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="H65">
-        <v>38.02</v>
+        <v>28.57</v>
       </c>
       <c r="I65">
-        <v>58.62</v>
+        <v>41.69</v>
       </c>
       <c r="J65">
-        <v>54.17</v>
+        <v>45.91</v>
       </c>
       <c r="K65">
-        <v>1.63</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="2">
-        <v>45949.77083333334</v>
+        <v>45986.89583333334</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66">
+        <v>3.9</v>
+      </c>
+      <c r="G66">
         <v>2.4</v>
       </c>
-      <c r="G66">
-        <v>1.88</v>
-      </c>
       <c r="H66">
-        <v>41.67</v>
+        <v>25.64</v>
       </c>
       <c r="I66">
-        <v>53.31</v>
+        <v>41.71</v>
       </c>
       <c r="J66">
-        <v>27.93</v>
+        <v>62.68</v>
       </c>
       <c r="K66">
         <v>-1</v>
@@ -2792,139 +2792,139 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="2">
-        <v>45950.79166666666</v>
+        <v>45989.79166666666</v>
       </c>
       <c r="B67" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" t="s">
         <v>28</v>
       </c>
-      <c r="C67" t="s">
-        <v>25</v>
-      </c>
       <c r="D67">
         <v>1</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G67">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="H67">
-        <v>31.25</v>
+        <v>30.3</v>
       </c>
       <c r="I67">
-        <v>41.2</v>
+        <v>48.29</v>
       </c>
       <c r="J67">
-        <v>31.83</v>
+        <v>59.36</v>
       </c>
       <c r="K67">
-        <v>2.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="2">
-        <v>45950.8125</v>
+        <v>45993.89583333334</v>
       </c>
       <c r="B68" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F68">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="G68">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="H68">
-        <v>30.3</v>
+        <v>33.9</v>
       </c>
       <c r="I68">
-        <v>37.13</v>
+        <v>42.58</v>
       </c>
       <c r="J68">
-        <v>22.53</v>
+        <v>25.6</v>
       </c>
       <c r="K68">
-        <v>2.3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="2">
-        <v>45955.8125</v>
+        <v>45994.8125</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C69" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F69">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="G69">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="H69">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="I69">
-        <v>51.21</v>
+        <v>50.4</v>
       </c>
       <c r="J69">
-        <v>168.84</v>
+        <v>177.22</v>
       </c>
       <c r="K69">
-        <v>4.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="2">
-        <v>45956.85416666666</v>
+        <v>45994.89583333334</v>
       </c>
       <c r="B70" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C70" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F70">
-        <v>1.65</v>
+        <v>3.7</v>
       </c>
       <c r="G70">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="H70">
-        <v>60.61</v>
+        <v>27.03</v>
       </c>
       <c r="I70">
-        <v>74.04000000000001</v>
+        <v>53.51</v>
       </c>
       <c r="J70">
-        <v>22.16</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="K70">
         <v>-1</v>
@@ -2932,34 +2932,34 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="2">
-        <v>45962.75</v>
+        <v>46050.79166666666</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C71" t="s">
         <v>29</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F71">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="G71">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="H71">
-        <v>42.55</v>
+        <v>33.33</v>
       </c>
       <c r="I71">
-        <v>56.44</v>
+        <v>54.54</v>
       </c>
       <c r="J71">
-        <v>32.62</v>
+        <v>63.63</v>
       </c>
       <c r="K71">
         <v>-1</v>
@@ -2967,104 +2967,104 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="2">
-        <v>45963.66666666666</v>
+        <v>46051.83333333334</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C72" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D72">
         <v>2</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>1.79</v>
       </c>
       <c r="G72">
-        <v>2.33</v>
+        <v>1.46</v>
       </c>
       <c r="H72">
-        <v>33.33</v>
+        <v>55.87</v>
       </c>
       <c r="I72">
-        <v>42.97</v>
+        <v>68.36</v>
       </c>
       <c r="J72">
-        <v>28.92</v>
+        <v>22.36</v>
       </c>
       <c r="K72">
-        <v>2</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="2">
-        <v>45963.77083333334</v>
+        <v>46051.89583333334</v>
       </c>
       <c r="B73" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F73">
-        <v>6.25</v>
+        <v>2.3</v>
       </c>
       <c r="G73">
-        <v>4.3</v>
+        <v>1.86</v>
       </c>
       <c r="H73">
-        <v>16</v>
+        <v>43.48</v>
       </c>
       <c r="I73">
-        <v>23.25</v>
+        <v>53.87</v>
       </c>
       <c r="J73">
-        <v>45.33</v>
+        <v>23.91</v>
       </c>
       <c r="K73">
-        <v>-1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="2">
-        <v>45963.85416666666</v>
+        <v>46057.83333333334</v>
       </c>
       <c r="B74" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C74" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="G74">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="H74">
-        <v>44.44</v>
+        <v>45.45</v>
       </c>
       <c r="I74">
-        <v>56.79</v>
+        <v>70.87</v>
       </c>
       <c r="J74">
-        <v>27.78</v>
+        <v>55.91</v>
       </c>
       <c r="K74">
         <v>-1</v>
@@ -3072,69 +3072,69 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="2">
-        <v>45966.79166666666</v>
+        <v>46063.89583333334</v>
       </c>
       <c r="B75" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D75">
         <v>1</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F75">
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="G75">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="H75">
-        <v>40</v>
+        <v>17.39</v>
       </c>
       <c r="I75">
-        <v>48.24</v>
+        <v>38.22</v>
       </c>
       <c r="J75">
-        <v>20.61</v>
+        <v>119.77</v>
       </c>
       <c r="K75">
-        <v>1.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="2">
-        <v>45966.83333333334</v>
+        <v>46064.79166666666</v>
       </c>
       <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="s">
         <v>22</v>
       </c>
-      <c r="C76" t="s">
-        <v>20</v>
-      </c>
       <c r="D76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="G76">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="H76">
-        <v>29.41</v>
+        <v>41.67</v>
       </c>
       <c r="I76">
-        <v>42.7</v>
+        <v>55.49</v>
       </c>
       <c r="J76">
-        <v>45.17</v>
+        <v>33.17</v>
       </c>
       <c r="K76">
         <v>-1</v>
@@ -3142,34 +3142,34 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="2">
-        <v>45966.89583333334</v>
+        <v>46065.89583333334</v>
       </c>
       <c r="B77" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="G77">
-        <v>3.07</v>
+        <v>2.12</v>
       </c>
       <c r="H77">
-        <v>21.05</v>
+        <v>32.26</v>
       </c>
       <c r="I77">
-        <v>32.62</v>
+        <v>47.25</v>
       </c>
       <c r="J77">
-        <v>54.96</v>
+        <v>46.46</v>
       </c>
       <c r="K77">
         <v>-1</v>
@@ -3177,104 +3177,104 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="2">
-        <v>45970.85416666666</v>
+        <v>46078.79166666666</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C78" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="G78">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="H78">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="I78">
-        <v>37.09</v>
+        <v>48.03</v>
       </c>
       <c r="J78">
-        <v>48.37</v>
+        <v>56.09</v>
       </c>
       <c r="K78">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="2">
-        <v>45976.77083333334</v>
+        <v>46079.79166666666</v>
       </c>
       <c r="B79" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C79" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F79">
-        <v>7.5</v>
+        <v>2.01</v>
       </c>
       <c r="G79">
-        <v>5.31</v>
+        <v>1.52</v>
       </c>
       <c r="H79">
-        <v>13.33</v>
+        <v>49.75</v>
       </c>
       <c r="I79">
-        <v>18.82</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="J79">
-        <v>41.18</v>
+        <v>32.52</v>
       </c>
       <c r="K79">
-        <v>-1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="2">
-        <v>45981.66666666666</v>
+        <v>46093.79166666666</v>
       </c>
       <c r="B80" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C80" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F80">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G80">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="H80">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="I80">
-        <v>40.21</v>
+        <v>42.72</v>
       </c>
       <c r="J80">
-        <v>40.73</v>
+        <v>70.89</v>
       </c>
       <c r="K80">
         <v>-1</v>
@@ -3282,69 +3282,69 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="2">
-        <v>45986.89583333334</v>
+        <v>46093.8125</v>
       </c>
       <c r="B81" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81">
         <v>1</v>
       </c>
       <c r="F81">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="G81">
-        <v>3.03</v>
+        <v>2.17</v>
       </c>
       <c r="H81">
-        <v>25.64</v>
+        <v>32.26</v>
       </c>
       <c r="I81">
-        <v>32.97</v>
+        <v>46.18</v>
       </c>
       <c r="J81">
-        <v>28.6</v>
+        <v>43.14</v>
       </c>
       <c r="K81">
-        <v>-1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="2">
-        <v>45989.79166666666</v>
+        <v>46095.85416666666</v>
       </c>
       <c r="B82" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C82" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="G82">
-        <v>2.53</v>
+        <v>2.17</v>
       </c>
       <c r="H82">
-        <v>30.3</v>
+        <v>24.39</v>
       </c>
       <c r="I82">
-        <v>39.5</v>
+        <v>46.1</v>
       </c>
       <c r="J82">
-        <v>30.33</v>
+        <v>89.02</v>
       </c>
       <c r="K82">
         <v>-1</v>
@@ -3352,69 +3352,69 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="2">
-        <v>45993.89583333334</v>
+        <v>46099.89583333334</v>
       </c>
       <c r="B83" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83">
         <v>2</v>
       </c>
       <c r="F83">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="G83">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="H83">
-        <v>33.9</v>
+        <v>27.03</v>
       </c>
       <c r="I83">
-        <v>41.52</v>
+        <v>48.37</v>
       </c>
       <c r="J83">
-        <v>22.49</v>
+        <v>78.97</v>
       </c>
       <c r="K83">
-        <v>-1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="2">
-        <v>45994.8125</v>
+        <v>46100.89583333334</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C84" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F84">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="G84">
-        <v>2.14</v>
+        <v>2.39</v>
       </c>
       <c r="H84">
-        <v>18.18</v>
+        <v>29.41</v>
       </c>
       <c r="I84">
-        <v>46.66</v>
+        <v>41.9</v>
       </c>
       <c r="J84">
-        <v>156.64</v>
+        <v>42.47</v>
       </c>
       <c r="K84">
         <v>-1</v>
@@ -3422,36 +3422,65 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="2">
-        <v>45994.89583333334</v>
+        <v>46102.875</v>
       </c>
       <c r="B85" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C85" t="s">
+        <v>29</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>2.75</v>
+      </c>
+      <c r="G85">
+        <v>1.87</v>
+      </c>
+      <c r="H85">
+        <v>36.36</v>
+      </c>
+      <c r="I85">
+        <v>53.35</v>
+      </c>
+      <c r="J85">
+        <v>46.7</v>
+      </c>
+      <c r="K85">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="2">
+        <v>46103.66666666666</v>
+      </c>
+      <c r="B86" t="s">
         <v>31</v>
       </c>
-      <c r="D85">
-        <v>0</v>
-      </c>
-      <c r="E85">
-        <v>3</v>
-      </c>
-      <c r="F85">
-        <v>3.7</v>
-      </c>
-      <c r="G85">
-        <v>2</v>
-      </c>
-      <c r="H85">
-        <v>27.03</v>
-      </c>
-      <c r="I85">
-        <v>49.96</v>
-      </c>
-      <c r="J85">
-        <v>84.84999999999999</v>
-      </c>
-      <c r="K85">
+      <c r="C86" t="s">
+        <v>28</v>
+      </c>
+      <c r="F86">
+        <v>3.8</v>
+      </c>
+      <c r="G86">
+        <v>2.55</v>
+      </c>
+      <c r="H86">
+        <v>26.32</v>
+      </c>
+      <c r="I86">
+        <v>39.18</v>
+      </c>
+      <c r="J86">
+        <v>48.88</v>
+      </c>
+      <c r="K86">
         <v>-1</v>
       </c>
     </row>
